--- a/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01J70BR39BAVVVV4MTDG7T04J6</t>
+          <t>h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01J70BR39BAVVVV4MTDG7T04J6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
         </is>
       </c>
     </row>
@@ -473,12 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HAYYM66WATF77B0B4</t>
+          <t>h_01KV523N864ATFG7JMDXFT5DG6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K06FVR3HAYYM66WATF77B0B4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV523N864ATFG7JMDXFT5DG6</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
     </row>
@@ -551,29 +551,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01KV57ZG85Y9KNEXG8S288H3WK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV57ZG85Y9KNEXG8S288H3WK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,254 +583,100 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JYRFK57MP32WBT9QFD5S1R1B</t>
+          <t>h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JYRFK57MP32WBT9QFD5S1R1B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Company Data Sync</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K09DX9KGEJCSVX6XJ3DJCFYT</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K09DX9KGEJCSVX6XJ3DJCFYT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Department Sync</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K09DX9KGM7QHCFQA00E54Z1D</t>
+          <t>h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K09DX9KGM7QHCFQA00E54Z1D</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Location Sync</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>h_01JYRFQ5MFAA2PZ3GWN30PECXY</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JYRFQ5MFAA2PZ3GWN30PECXY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Position Sync</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>h_01JYRFQ5MFNQ50411TFSTYGHBN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01JYRFQ5MFNQ50411TFSTYGHBN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Manager Sync</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>h_01K09EMH8GFXM2PAWRWKYHQGWD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K09EMH8GFXM2PAWRWKYHQGWD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Attribute Mapping</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>h_01K09DX9KGJWGXTRTCDHE1MA6Y</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K09DX9KGJWGXTRTCDHE1MA6Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>
       </c>
     </row>

--- a/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,42 +639,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Target Application</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KV5AWNTPZPYF77BM6DAABDME</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV5AWNTPZPYF77BM6DAABDME</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Lifecycle Event</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KV5DGBF812MM5BKGE37A93MK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV5DGBF812MM5BKGE37A93MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Event Configuration</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KV5M76XT6PD9SQD744GWQ7T7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV5M76XT6PD9SQD744GWQ7T7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>

--- a/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,20 +727,218 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Notification Delivery Channel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KV83VHYFNQ9B9RMXYKQ8AP58</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV83VHYFNQ9B9RMXYKQ8AP58</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KV83VHYFMMCWYEXHZDYHNQ3P</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV83VHYFMMCWYEXHZDYHNQ3P</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV580TKT6XVZ3JH5D9VWKF9J</t>
         </is>

--- a/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/headings.xlsx
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KV83VHYFNQ9B9RMXYKQ8AP58</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV83VHYFNQ9B9RMXYKQ8AP58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KV83VHYFMMCWYEXHZDYHNQ3P</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV83VHYFMMCWYEXHZDYHNQ3P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-ServiceNow-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
